--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1106521.5</v>
+        <v>1182.56</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>531690.8100000001</v>
+        <v>568.23</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8919330.84</v>
+        <v>9532.280000000001</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>687267.84</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5955224.1</v>
+        <v>6364.48</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1086351</v>
+        <v>1161.01</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10377634.19</v>
+        <v>11090.8</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7004449.48</v>
+        <v>7485.81</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2341634.4</v>
+        <v>2502.55</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8138.94</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8683239.6</v>
+        <v>9279.959999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8197983.78</v>
+        <v>8761.360000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>595098.77</v>
+        <v>635.99</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>371731.01</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8670331.67</v>
+        <v>9266.17</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>321025.11</v>
+        <v>343.09</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8072517.32</v>
+        <v>8627.27</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1803706.8</v>
+        <v>1927.66</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8366604.4</v>
+        <v>8941.57</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>33981997</v>
+        <v>36317.29</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8072517.32</v>
+        <v>8627.27</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>34379100</v>
+        <v>36741.68</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>240825.06</v>
+        <v>257.37</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>23562000</v>
+        <v>25181.22</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13989394.86</v>
+        <v>14950.77</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>642983.1800000001</v>
+        <v>687.17</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>114537.5</v>
+        <v>122.41</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>519958.6</v>
+        <v>555.6900000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>354620</v>
+        <v>378.99</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6849543.61</v>
+        <v>7320.25</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8069.53</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4814145</v>
+        <v>5144.98</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16707243</v>
+        <v>17855.39</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8692716.76</v>
+        <v>9290.09</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10589760.02</v>
+        <v>11317.5</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13342691.74</v>
+        <v>14259.62</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9094732.08</v>
+        <v>9719.74</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>850758.37</v>
+        <v>909.22</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>506842.42</v>
+        <v>541.67</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1828646.82</v>
+        <v>1954.31</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>609991.62</v>
+        <v>651.91</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8069.53</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>567606.2</v>
+        <v>606.61</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2043556.06</v>
+        <v>2183.99</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>23930766.72</v>
+        <v>25575.32</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8371669.04</v>
+        <v>8946.98</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>458479.63</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>709185.26</v>
+        <v>757.92</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>715190</v>
+        <v>764.34</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6479550</v>
+        <v>6924.83</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>754275.55</v>
+        <v>806.11</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>457107.56</v>
+        <v>488.52</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1275918</v>
+        <v>1363.6</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3209430</v>
+        <v>3429.99</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3025813</v>
+        <v>3233.75</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>18369177.96</v>
+        <v>19631.53</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7536865</v>
+        <v>8054.81</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4316322.78</v>
+        <v>4612.95</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2496367.72</v>
+        <v>2667.92</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4331481</v>
+        <v>4629.15</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10042374.3</v>
+        <v>10732.5</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6767613.3</v>
+        <v>7232.69</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>523267.99</v>
+        <v>559.23</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>534014.88</v>
+        <v>570.71</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>241992.45</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8249315.62</v>
+        <v>8816.219999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2522800</v>
+        <v>2696.17</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5311231.8</v>
+        <v>5676.23</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8488973.289999999</v>
+        <v>9072.35</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>458927.07</v>
+        <v>490.47</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>33629995</v>
+        <v>35941.1</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8465759.960000001</v>
+        <v>9047.540000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>933894.15</v>
+        <v>998.0700000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>16931519.92</v>
+        <v>18095.08</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>897885.9399999999</v>
+        <v>959.59</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>13883730</v>
+        <v>14837.84</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7398230</v>
+        <v>7906.65</v>
       </c>
     </row>
     <row r="100">
@@ -6543,11 +6543,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8138.94</v>
       </c>
     </row>
     <row r="101">
@@ -6604,11 +6604,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2214360.33</v>
+        <v>2366.53</v>
       </c>
     </row>
     <row r="102">
@@ -6665,11 +6665,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="103">
@@ -6726,11 +6726,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6787,11 +6787,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>547047.76</v>
+        <v>584.64</v>
       </c>
     </row>
     <row r="105">
@@ -6848,11 +6848,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="106">
@@ -6909,11 +6909,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>17076500</v>
+        <v>18250.02</v>
       </c>
     </row>
     <row r="107">
@@ -6970,11 +6970,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8558.51</v>
       </c>
     </row>
     <row r="108">
@@ -7031,11 +7031,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3210910.36</v>
+        <v>3431.57</v>
       </c>
     </row>
     <row r="109">
@@ -7092,11 +7092,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>534014.88</v>
+        <v>570.71</v>
       </c>
     </row>
     <row r="110">
@@ -7153,11 +7153,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4523190</v>
+        <v>4834.03</v>
       </c>
     </row>
     <row r="111">
@@ -7214,11 +7214,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>493529.89</v>
+        <v>527.45</v>
       </c>
     </row>
     <row r="112">
@@ -7275,11 +7275,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7336,11 +7336,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3255329.49</v>
+        <v>3479.04</v>
       </c>
     </row>
     <row r="114">
@@ -7397,11 +7397,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>9669874.550000001</v>
+        <v>10334.4</v>
       </c>
     </row>
     <row r="115">
@@ -7458,11 +7458,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9938880</v>
+        <v>10621.89</v>
       </c>
     </row>
     <row r="116">
@@ -7519,11 +7519,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>534862.16</v>
+        <v>571.62</v>
       </c>
     </row>
     <row r="117">
@@ -7580,11 +7580,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7641,11 +7641,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>600700.1</v>
+        <v>641.98</v>
       </c>
     </row>
     <row r="119">
@@ -7702,11 +7702,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1686613.18</v>
+        <v>1802.52</v>
       </c>
     </row>
     <row r="120">
@@ -7763,11 +7763,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8072680.35</v>
+        <v>8627.450000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7824,11 +7824,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1932238.7</v>
+        <v>2065.02</v>
       </c>
     </row>
     <row r="122">
@@ -7885,11 +7885,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="123">
@@ -7946,11 +7946,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>22912498</v>
+        <v>24487.08</v>
       </c>
     </row>
     <row r="124">
@@ -8007,11 +8007,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>478822.68</v>
+        <v>511.73</v>
       </c>
     </row>
     <row r="125">
@@ -8068,11 +8068,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="126">
@@ -8129,11 +8129,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8683239.6</v>
+        <v>9279.959999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8190,11 +8190,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>979101.0600000001</v>
+        <v>1046.39</v>
       </c>
     </row>
     <row r="128">
@@ -8251,11 +8251,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="129">
@@ -8312,11 +8312,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="130">
@@ -8373,11 +8373,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>413015.68</v>
+        <v>441.4</v>
       </c>
     </row>
     <row r="131">
@@ -8434,11 +8434,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7539419.93</v>
+        <v>8057.54</v>
       </c>
     </row>
     <row r="132">
@@ -8495,11 +8495,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>118515.67</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="133">
@@ -8556,11 +8556,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7626839.71</v>
+        <v>8150.97</v>
       </c>
     </row>
     <row r="134">
@@ -8617,11 +8617,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="135">
@@ -8678,11 +8678,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8610.610000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8739,11 +8739,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8800,11 +8800,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>693076.23</v>
+        <v>740.71</v>
       </c>
     </row>
     <row r="138">
@@ -8861,11 +8861,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="139">
@@ -8922,11 +8922,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="140">
@@ -8983,11 +8983,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="141">
@@ -9044,11 +9044,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9105,11 +9105,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="143">
@@ -9166,11 +9166,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>941831.45</v>
+        <v>1006.56</v>
       </c>
     </row>
     <row r="144">
@@ -9227,11 +9227,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1932560</v>
+        <v>2065.37</v>
       </c>
     </row>
     <row r="145">
@@ -9288,11 +9288,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>152755.54</v>
+        <v>163.25</v>
       </c>
     </row>
     <row r="146">
@@ -9349,11 +9349,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>34485616.9</v>
+        <v>36855.52</v>
       </c>
     </row>
     <row r="147">
@@ -9410,11 +9410,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="148">
@@ -9471,11 +9471,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="149">
@@ -9532,11 +9532,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8197742.21</v>
+        <v>8761.1</v>
       </c>
     </row>
     <row r="150">
@@ -9593,11 +9593,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2369404.24</v>
+        <v>2532.23</v>
       </c>
     </row>
     <row r="151">
@@ -9654,11 +9654,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3593819.04</v>
+        <v>3840.79</v>
       </c>
     </row>
     <row r="152">
@@ -9715,11 +9715,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8197742.21</v>
+        <v>8761.1</v>
       </c>
     </row>
     <row r="153">
@@ -9776,11 +9776,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3728879.28</v>
+        <v>3985.13</v>
       </c>
     </row>
     <row r="154">
@@ -9837,11 +9837,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="155">
@@ -9898,11 +9898,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>624400.14</v>
+        <v>667.3099999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9959,11 +9959,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="157">
@@ -10020,11 +10020,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="158">
@@ -10081,11 +10081,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="159">
@@ -10142,11 +10142,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="160">
@@ -10203,11 +10203,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>840796.88</v>
+        <v>898.58</v>
       </c>
     </row>
     <row r="161">
@@ -10264,11 +10264,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3343495.4</v>
+        <v>3573.27</v>
       </c>
     </row>
     <row r="162">
@@ -10325,11 +10325,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>102868.36</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="163">
@@ -10386,11 +10386,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8558.51</v>
       </c>
     </row>
     <row r="164">
@@ -10447,11 +10447,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1944460</v>
+        <v>2078.09</v>
       </c>
     </row>
     <row r="165">
@@ -10508,11 +10508,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9372.620000000001</v>
       </c>
     </row>
     <row r="166">
@@ -10569,11 +10569,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>420399.63</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="167">
@@ -10630,11 +10630,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8558.51</v>
       </c>
     </row>
     <row r="168">
@@ -10691,11 +10691,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8150.11</v>
       </c>
     </row>
     <row r="169">
@@ -10752,11 +10752,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>420398.44</v>
+        <v>449.29</v>
       </c>
     </row>
     <row r="170">
@@ -10813,11 +10813,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8138.94</v>
       </c>
     </row>
     <row r="171">
@@ -10874,11 +10874,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5814416.16</v>
+        <v>6213.99</v>
       </c>
     </row>
     <row r="172">
@@ -10935,11 +10935,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>10276483</v>
+        <v>10982.7</v>
       </c>
     </row>
     <row r="173">
@@ -10996,11 +10996,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8683239.6</v>
+        <v>9279.959999999999</v>
       </c>
     </row>
     <row r="174">
@@ -11057,11 +11057,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>628772.2</v>
+        <v>671.98</v>
       </c>
     </row>
     <row r="175">
@@ -11118,11 +11118,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>9938833.59</v>
+        <v>10621.84</v>
       </c>
     </row>
   </sheetData>
